--- a/tests/data_golden/values.template.xlsx
+++ b/tests/data_golden/values.template.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="39">
   <si>
     <t>values-path</t>
   </si>
@@ -145,6 +145,12 @@
   </si>
   <si>
     <t>${#c}</t>
+  </si>
+  <si>
+    <t>values-edge-space</t>
+  </si>
+  <si>
+    <t>${vspace}</t>
   </si>
 </sst>
 </file>
@@ -915,6 +921,14 @@
         <v>23</v>
       </c>
     </row>
+    <row r="14">
+      <c r="B14" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" t="s">
+        <v>38</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
